--- a/Result/profitability/6166.xlsx
+++ b/Result/profitability/6166.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6987500000000001</v>
+        <v>0.87</v>
       </c>
       <c r="N2" t="n">
-        <v>37.91875</v>
+        <v>37.0675</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>0.78</v>
+        <v>0.8712500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>38.61625</v>
+        <v>38.06375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>0.75</v>
+        <v>0.905</v>
       </c>
       <c r="N4" t="n">
-        <v>39.36</v>
+        <v>39.07875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7225</v>
+        <v>0.92625</v>
       </c>
       <c r="N5" t="n">
-        <v>39.8375</v>
+        <v>39.5075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7575</v>
+        <v>0.79</v>
       </c>
       <c r="N6" t="n">
-        <v>41.00375</v>
+        <v>40.445</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.61125</v>
+        <v>0.7012499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>42.47625</v>
+        <v>41.92125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5475</v>
+        <v>0.5449999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>42.605</v>
+        <v>41.94125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6166</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4459</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3022</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1438</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>482</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.81%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>478</v>
+      </c>
+      <c r="K75" t="n">
+        <v>337</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8087500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.0325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.01273885350318471</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.309999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1414114513981357</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-20.375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.640000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07568807339449546</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
